--- a/Altium/TDR/TDR_BOM.xlsx
+++ b/Altium/TDR/TDR_BOM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="194">
   <si>
     <t>Name/Value</t>
   </si>
@@ -40,27 +40,18 @@
     <t>Supplier Part Number 1</t>
   </si>
   <si>
-    <t>Link 1</t>
-  </si>
-  <si>
     <t>Supplier 2</t>
   </si>
   <si>
     <t>Supplier Part Number 2</t>
   </si>
   <si>
-    <t>Link 2</t>
-  </si>
-  <si>
     <t>Supplier 3</t>
   </si>
   <si>
     <t>Supplier Part Number 4</t>
   </si>
   <si>
-    <t>Link 3</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -88,18 +79,12 @@
     <t>80-C0603C106M9P7411</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/c/passive-components/capacitors/ceramic-capacitors/mlccs-multilayer-ceramic-capacitors/multilayer-ceramic-capacitors-mlcc-smd-smt/?capacitance=10%20uF&amp;case%20code%20-%20in=0603&amp;dielectric=X5R&amp;tolerance=20%20%25&amp;srsltid=AfmBOop5FtOSLBANALFOKim3Y4haiHYs_K6iaUN6Tylxu6BKO6MrjJRp</t>
-  </si>
-  <si>
     <t>DigiKey</t>
   </si>
   <si>
     <t>399-C0603C106M9PAC7411TR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/kemet/C0603C106M9PAC7411/18121140</t>
-  </si>
-  <si>
     <t>Generic</t>
   </si>
   <si>
@@ -127,24 +112,15 @@
     <t>581-KGQ15ACG2D100GT</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/KYOCERA-AVX/KGQ15ACG2D100GT?qs=Jm2GQyTW%2FbjQ2Gx%252Bxx6sLQ%3D%3D</t>
-  </si>
-  <si>
     <t>478-KGQ15ACG2D100GTTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.at/en/products/detail/kyocera-avx/KGQ15ACG2D100GT/1598982?srsltid=AfmBOoo2LOxQau7947xBCUB6vTniU6z5pl54Ir7OnnbfIl6n8-OXc0lF</t>
-  </si>
-  <si>
     <t>arrow electronics</t>
   </si>
   <si>
     <t>Cap Ceramic 10pF 200V C0G 2% Pad SMD 0603 125°C T/R</t>
   </si>
   <si>
-    <t>https://www.arrow.com/en/products/kgq15acg2d100gt/avx</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -154,7 +130,7 @@
     <t>Low ESR Decoupling capacitor</t>
   </si>
   <si>
-    <t>C6, C12, C13, C14, C15, C16, C17, C18, C19, C29, C30, C37, C38, C40 C42</t>
+    <t>C6, C12, C13, C14, C15, C16, C17, C18, C19,C28, C29, C37, C38, C40 C42</t>
   </si>
   <si>
     <t>KGM15AR70J104KT</t>
@@ -163,22 +139,16 @@
     <t>581-KGM15AR70J104KT</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/KYOCERA-AVX/KGM15AR70J104KT?qs=OcgtsXO%252B3gtdv8uwlMb47g%3D%3D&amp;srsltid=AfmBOoqR-Uq0VaORAg4huXcShwUfmslmtyEy8at5XPXHFWa-6C1ibQaV</t>
-  </si>
-  <si>
     <t>478-KGM15AR70J104KTTR-ND -</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/kyocera-avx/KGM15AR70J104KT/1600415</t>
-  </si>
-  <si>
     <t>Generic Low ESR</t>
   </si>
   <si>
     <t>100pF</t>
   </si>
   <si>
-    <t>C7, C8, C9, C10, C11, C20, C21, C22, C32, C33, C34, C39</t>
+    <t>C7, C8, C9, C10, C11, C20, C21, C22, C32, C33, C34,</t>
   </si>
   <si>
     <t>KGM15ACG2A101JM</t>
@@ -187,18 +157,12 @@
     <t>581-KGM15ACG2A101JM</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/KYOCERA-AVX/KGM15ACG2A101JM?qs=Jm2GQyTW%2FbjQIVGu7Y2CGA%3D%3D&amp;utm_id=9882661914&amp;utm_source=google&amp;utm_medium=cpc&amp;utm_marketing_tactic=emeacorp&amp;gad_source=1&amp;gad_campaignid=9882661914&amp;gclid=Cj0KCQiAwYrNBhDcARIsAGo3u30-cMxq_qCD5f1XKRs-woKgiE3Fz7VslSv9frryQmxLOYgwNUw8S2UaAnEDEALw_wcB</t>
-  </si>
-  <si>
     <t>ElectroMaker</t>
   </si>
   <si>
     <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 100V 100pF C0G 0603 5%</t>
   </si>
   <si>
-    <t>https://www.electromaker.io/shop/product/100v-100pf-c0g-0603-5?srsltid=AfmBOoonytzA0TxyNjHEGATYr29xolq-ne7FNUstguxHA-_BxwVcFrcH</t>
-  </si>
-  <si>
     <t>100uF</t>
   </si>
   <si>
@@ -211,60 +175,48 @@
     <t>THT</t>
   </si>
   <si>
-    <t>Pansonic</t>
-  </si>
-  <si>
-    <t>EEU-FR1J101B</t>
-  </si>
-  <si>
-    <t>667-EEU-FR1J101B</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/Panasonic/EEU-FR1J101B?qs=sGAEpiMZZMvwFf0viD3Y3UQZTqF4ErAnC%2FgAohLjJuY%3D</t>
-  </si>
-  <si>
-    <t>P15287CT-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/panasonic-electronic-components/EEU-FR1J101B/3072304</t>
+    <t>Kemet</t>
+  </si>
+  <si>
+    <t>ESK107M025AC3AA</t>
+  </si>
+  <si>
+    <t>80-ESK107M025AC3AA</t>
+  </si>
+  <si>
+    <t>399-6102-ND</t>
+  </si>
+  <si>
+    <t>Newark</t>
+  </si>
+  <si>
+    <t>87AC7446</t>
+  </si>
+  <si>
+    <t>SMF5.0A-T13</t>
+  </si>
+  <si>
+    <t>TVS Diode (Uni-directional)</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SOD-123-2</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>576-SMF5.0A-T13</t>
+  </si>
+  <si>
+    <t>18-SMF5.0A-T13TR-ND</t>
   </si>
   <si>
     <t>Farnell</t>
   </si>
   <si>
-    <t>https://uk.farnell.com/panasonic/eeufr1j101b/cap-100-f-63v-20/dp/2079295</t>
-  </si>
-  <si>
-    <t>SMF5.0A-T13</t>
-  </si>
-  <si>
-    <t>TVS Diode (Uni-directional)</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>SOD-123-2</t>
-  </si>
-  <si>
-    <t>Littelfuse</t>
-  </si>
-  <si>
-    <t>576-SMF5.0A-T13</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/Littelfuse/SMF5.0A-T13?qs=aGgfWYEhH7lEohru0mAWAg%3D%3D&amp;srsltid=AfmBOoq7EN53faBMAcJUTOow40NiAMWXeJ94GOEt5SF1fkf92PWU2pNw</t>
-  </si>
-  <si>
-    <t>18-SMF5.0A-T13TR-ND</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/littelfuse-inc/SMF5-0A-T13/5235573</t>
-  </si>
-  <si>
-    <t>https://pl.farnell.com/littelfuse/smf5-0a/tvs-diode-200w-5v-unidir-sod-123fl/dp/2691565?srsltid=AfmBOorzR-wBBikzZ4auDqsrArdD_KK5C7gNZHqkwbmcoBebTQWaWhEB</t>
-  </si>
-  <si>
     <t>TLMG1100-GS15</t>
   </si>
   <si>
@@ -280,21 +232,12 @@
     <t>78-TLMG1100-GS15</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Vishay-Semiconductors/TLMG1100-GS15?qs=vvQtp7zwQdObPNLeC1kn7g%3D%3D&amp;srsltid=AfmBOoqgextsrg3UJ_b2Fhr5h5YaRLJ387XqdifJ6tQGKuEfOLTa-_V-</t>
-  </si>
-  <si>
     <t>751-TLMG1100-GS15TR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/vishay-semiconductor-opto-division/TLMG1100-GS15/16652837?srsltid=AfmBOopzI16ksS6yNxlDxGttKekD-OYxBXHPCXXDcqsSuCHw44GZ0VBP</t>
-  </si>
-  <si>
     <t>TME</t>
   </si>
   <si>
-    <t>https://www.tme.eu/pl/details/tlmg1100-gs15/diody-led-smd-kolorowe/vishay/?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=Optoelektronika%20PL%20%5BP%5D%5BSA%5D&amp;utm_content=&amp;campaign_id=22521994535&amp;gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=22521994535&amp;gclid=Cj0KCQiA5I_NBhDVARIsAOrqIsYoDKwg2__3izeiw7WO0mT9vOVXvQhsZXiKlZWgxXEzQF1bGinGdPwaAscnEALw_wcB</t>
-  </si>
-  <si>
     <t>AQ4020-01FTG</t>
   </si>
   <si>
@@ -307,24 +250,15 @@
     <t>576-AQ4020-01FTG</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Littelfuse/AQ4020-01FTG?qs=YCa%2FAAYMW015W3B84qpvIw%3D%3D&amp;srsltid=AfmBOorXlOMEIL0Qu2pjxoVN8XCcBI55zf1bU0myG2tp7FXa5e1EkX_D</t>
-  </si>
-  <si>
     <t>F10395TR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/littelfuse-inc/AQ4020-01FTG-C/7902198?srsltid=AfmBOop6gDsCeufE8RpYJdLAz1t7vJvA1Doxugbtou_2OzXFQoBkQU_d</t>
-  </si>
-  <si>
     <t>Arrow Electronics</t>
   </si>
   <si>
     <t>ESD Suppressor Diode TVS Bi-Dir 3.3V 24.5Vc Automotive AEC-Q101 2-Pin SOD-323 T/R</t>
   </si>
   <si>
-    <t>https://www.arrow.com/en/products/aq4020-01ftg-c/littelfuse</t>
-  </si>
-  <si>
     <t>142-0701-851</t>
   </si>
   <si>
@@ -364,21 +298,12 @@
     <t>651-1803426</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Phoenix-Contact/1803426?qs=Xflg4jNzfa4gkEMgYX0Czg%3D%3D&amp;srsltid=AfmBOorToPc-X-i6NHzWIq2REtEW38JzMnG8wYkY-EBSLOfxchr5Di47</t>
-  </si>
-  <si>
     <t>277-1221-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/phoenix-contact/1803426/260589?srsltid=AfmBOoqhFKSeEHPbYwgyUpg9A4KGJlJVbGmsLSvrl5BPvyB8tOTWkt_7</t>
-  </si>
-  <si>
     <t>MCV1.5/2-G-3.81</t>
   </si>
   <si>
-    <t>https://www.tme.eu/pl/details/mcv1.5_2-g-3.81/listwy-zaciskowe-rozlaczalne/phoenix-contact/1803426/</t>
-  </si>
-  <si>
     <t>Generic THT Vertical Pin Header WR-PHD, Pitch 2.54 mm, Single Row, 9 pins</t>
   </si>
   <si>
@@ -394,12 +319,6 @@
     <t>710-61300911121</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Wurth-Elektronik/61300911121?qs=PhR8RmCirEZgp0mLtcLaGw%3D%3D&amp;srsltid=AfmBOoprKALJRQA80-w-ZaRhfuRESMQqflewejWQdC_6rtEc4POqitbF</t>
-  </si>
-  <si>
-    <t>https://uk.farnell.com/wurth-elektronik/61300911121/header-2-54mm-pin-tht-vertical/dp/2356161</t>
-  </si>
-  <si>
     <t>Generic Goldpins 2.54mm rastr 9-10 pins</t>
   </si>
   <si>
@@ -421,18 +340,9 @@
     <t>621-DMP4015SK3-13</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Diodes-Incorporated/DMP4015SK3-13?qs=T%2FOtf55vL7fON%252BtWokt2Lw%3D%3D&amp;srsltid=AfmBOop40OewdBOI32zZ2tC8tssc_UE0t2Xrun5pMIk056witTHSo_PM</t>
-  </si>
-  <si>
     <t>DMP4015SK3-13DITR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/diodes-incorporated/DMP4015SK3-13/2792424?srsltid=AfmBOor1Mc8f4F7_PnmLOMCsfmadWQWsiyUuZDyRNqDRyhT_Olr9x6zP</t>
-  </si>
-  <si>
-    <t>https://pl.farnell.com/diodes-inc/dmp4015sk3-13/mosfet-p-ch-40v-to-252-3/dp/2543554?srsltid=AfmBOooXioDk8ZEeRfwKbd5pAso58Tays1RTHZ7K3PQdRw7ncahjEh8r</t>
-  </si>
-  <si>
     <t>91k</t>
   </si>
   <si>
@@ -451,16 +361,10 @@
     <t>603-RC0805FR-0791KL</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/RC0805FR-0791KL?qs=sGAEpiMZZMvdGkrng054t%252BrOXiwDHiXwO95v24P%2FJpk%3D</t>
-  </si>
-  <si>
     <t>311-91.0KCRTR-ND - Tape &amp; Reel</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/RC0805FR-0791KL/728202</t>
-  </si>
-  <si>
-    <t>R3, R18</t>
+    <t>R3, R18, R20, R21</t>
   </si>
   <si>
     <t>AC0805FR-070RL</t>
@@ -469,15 +373,9 @@
     <t>603-AC0805FR-070RL</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/AC0805FR-070RL?qs=sGAEpiMZZMvdGkrng054twVr7TWeaA0stZVp9zaHJmE%3D</t>
-  </si>
-  <si>
     <t>13-AC0805FR-070RLTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/AC0805FR-070RL/12698884</t>
-  </si>
-  <si>
     <t>1.2K</t>
   </si>
   <si>
@@ -490,15 +388,9 @@
     <t>603-AC0805FR-071K2L</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/AC0805FR-071K2L?qs=sGAEpiMZZMvdGkrng054t2uy2SOblyUPud%252BcKnFki4Y%3D</t>
-  </si>
-  <si>
     <t>YAG3700TR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/AC0805FR-071K2L/5896622</t>
-  </si>
-  <si>
     <t>33.2K</t>
   </si>
   <si>
@@ -511,15 +403,9 @@
     <t>603-AC0805FR-0733K2L</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/AC0805FR-0733K2L?qs=sGAEpiMZZMvdGkrng054twVr7TWeaA0sFISFnTE48t4%3D</t>
-  </si>
-  <si>
     <t>13-AC0805FR-0733K2LTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/AC0805FR-0733K2L/5896773</t>
-  </si>
-  <si>
     <t>R6, R7, R8</t>
   </si>
   <si>
@@ -532,15 +418,9 @@
     <t>71-RCP0603W50R0GEB</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Vishay-Dale/RCP0603W50R0GEB?qs=fKKhUIXmUuML9DdHVS1BYg%3D%3D&amp;srsltid=AfmBOoqyBtLbkvStHJ1jIht5VHOWlluNdAFePHIVHJrM335VOvlbDs7D</t>
-  </si>
-  <si>
     <t>541-2655-2-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/vishay-dale/RCP0603W50R0GEB/5481869</t>
-  </si>
-  <si>
     <t>R9</t>
   </si>
   <si>
@@ -550,15 +430,9 @@
     <t>603-RC0603FR-07100RL</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/RC0603FR-07100RL?qs=NEN%2FsE%2FLsvPIwIWKCOS4%2FA%3D%3D&amp;srsltid=AfmBOooEySiFn64E77m0v2kJDRyIhzBtI1XgVV3GeOm4saz-H31WWrCn</t>
-  </si>
-  <si>
     <t>311-100HRTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/yageo/RC0603FR-07100RL/726888?srsltid=AfmBOoqPGo7vkCWmJ6QXQlwWVpO7kbWc6tYnvR3KOivJsj0K0HtCTSyD</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
@@ -571,15 +445,9 @@
     <t>603-RC0805FR-0710KL</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/RC0805FR-0710KL?qs=sGAEpiMZZMvdGkrng054txqI5fKHz4dd6hDojai%2FwdI%3D</t>
-  </si>
-  <si>
     <t>311-10.0KCRTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/yageo/RC0805FR-0710KL/727535?srsltid=AfmBOormWcjwP9anNZm6Q3-7O6KkeW5-GmfavpLws9RZTRyaJoehsqn6</t>
-  </si>
-  <si>
     <t>R12, R13</t>
   </si>
   <si>
@@ -592,15 +460,9 @@
     <t>603-AC0603FR-07604RL</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/AC0603FR-07604RL?qs=sGAEpiMZZMvdGkrng054twVr7TWeaA0sHwVs%252BSg%252BmuI%3D</t>
-  </si>
-  <si>
     <t>13-AC0603FR-07604RLTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/AC0603FR-07604RL/5896224</t>
-  </si>
-  <si>
     <t>18.2K</t>
   </si>
   <si>
@@ -613,15 +475,9 @@
     <t>603-RC0805FR-0718K2L</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/YAGEO/RC0805FR-0718K2L?qs=sGAEpiMZZMvdGkrng054t3pr%252BPE%2FADjshkGrM7hkDdg%3D</t>
-  </si>
-  <si>
     <t>311-18.2KCRTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/RC0805FR-0718K2L/727646</t>
-  </si>
-  <si>
     <t>LT3045EDD#PBF</t>
   </si>
   <si>
@@ -640,24 +496,15 @@
     <t>584-LT3045EDD#PBF</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Analog-Devices/LT3045EDDPBF?qs=oahfZPh6IAItEW%2FaDCA8LQ%3D%3D&amp;srsltid=AfmBOopxD9IJrmXz_J8XeAL4S1Mr1E7jFpVegJCSVdIaC3McOE8F2UkH</t>
-  </si>
-  <si>
     <t>505-LT3045IDD#TRPBFTR-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.pl/pl/products/detail/analog-devices-inc/LT3045IDD-TRPBF/8024409</t>
-  </si>
-  <si>
     <t>Worldway Electronics</t>
   </si>
   <si>
     <t>LT3045EDD#PBF-10484781</t>
   </si>
   <si>
-    <t>https://www.worldwayelec.com/pro/analog-devices-inc/lt3045eddpbf/10484781?from=octopart</t>
-  </si>
-  <si>
     <t>SN65EPT22DGKR</t>
   </si>
   <si>
@@ -676,21 +523,12 @@
     <t>595-SN65EPT22DGKR</t>
   </si>
   <si>
-    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN65EPT22DGKR?qs=IDSsxkoac0wFl2SJxPZozQ%3D%3D&amp;srsltid=AfmBOor9niKN2PjQ84oS3ni-0vzBS5OkjDWpxU2PlpMEsZaYIyMUScIz</t>
-  </si>
-  <si>
     <t>296-46326-1-ND</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/texas-instruments/SN65EPT22DGKR/2047542</t>
-  </si>
-  <si>
     <t>Texas Industries</t>
   </si>
   <si>
-    <t>https://www.ti.com/product/SN65EPT22/part-details/SN65EPT22DGKR</t>
-  </si>
-  <si>
     <t>8T49N241-999NLGI</t>
   </si>
   <si>
@@ -700,6 +538,9 @@
     <t>U3</t>
   </si>
   <si>
+    <t>40-VFQFN</t>
+  </si>
+  <si>
     <t>Renesans electronics</t>
   </si>
   <si>
@@ -709,18 +550,9 @@
     <t>972-8T49N241-998NLGI</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Renesas-Electronics/8T49N241-998NLGI?qs=ZwKJWZfDtNhtUo1o1BMljQ%3D%3D</t>
-  </si>
-  <si>
-    <t>https://uk.farnell.com/integrated-device-technology/8t49n241-998nlgi/frequency-translator-40-to-85deg/dp/3251297</t>
-  </si>
-  <si>
     <t>RS</t>
   </si>
   <si>
-    <t>https://de.rs-online.com/web/p/takttreiber-und-taktverteilung/2166235?cm_mmc=aff2-_-de-_-octopart-_-2166235-_-instock&amp;gad_source=7&amp;gad_campaignid=14989544798&amp;dclid=CNDwrsDQ_pIDFXmJ_QcdGzkd3A</t>
-  </si>
-  <si>
     <t>5MS1S102AM2QE</t>
   </si>
   <si>
@@ -736,23 +568,38 @@
     <t>LIGHT COUNTRY CO., LTD</t>
   </si>
   <si>
-    <t>https://www.tme.eu/pl/details/5ms1s102am2qe/przelaczniki-suwakowe/light-country-co-ltd/</t>
-  </si>
-  <si>
     <t>118-5MS1S102AM2QES</t>
   </si>
   <si>
-    <t>https://www.mouser.pl/ProductDetail/Dailywell/5MS1S102AM2QES?qs=B6kkDfuK7%2FBAzQXswMG%252BOg%3D%3D&amp;srsltid=AfmBOop2BdFxlta8-cwmIxWzikhEPbLaeGArO84mt2XRlXERPHxbMuHf</t>
-  </si>
-  <si>
     <t>Generic SPDT switch with 4.7mm raster and at least 5A/20V</t>
+  </si>
+  <si>
+    <t>H130B-25.000-12-F-EXT-TR</t>
+  </si>
+  <si>
+    <t>Crystal 25MHZ, 12pF 30, mohm</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>SMD</t>
+  </si>
+  <si>
+    <t>Raltron Electronics</t>
+  </si>
+  <si>
+    <t>2151-H130B-25.000-12-F-EXT-TR-ND</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -766,17 +613,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font/>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
-    </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FF212529"/>
@@ -795,11 +635,6 @@
       <sz val="9.0"/>
       <color rgb="FF444444"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF212529"/>
-      <name val="ArrowDisplayRegular"/>
     </font>
   </fonts>
   <fills count="3">
@@ -844,6 +679,9 @@
       </bottom>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -852,9 +690,6 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -866,7 +701,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -876,53 +711,44 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1143,14 +969,13 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="34.38"/>
     <col customWidth="1" min="3" max="3" width="13.0"/>
-    <col customWidth="1" min="4" max="4" width="7.38"/>
+    <col customWidth="1" min="4" max="4" width="9.63"/>
     <col customWidth="1" min="5" max="5" width="4.38"/>
     <col customWidth="1" min="6" max="6" width="8.38"/>
     <col customWidth="1" min="7" max="7" width="8.88"/>
     <col customWidth="1" min="8" max="8" width="7.0"/>
     <col customWidth="1" min="9" max="9" width="9.13"/>
-    <col customWidth="1" min="10" max="10" width="4.88"/>
-    <col customWidth="1" min="12" max="12" width="8.25"/>
+    <col customWidth="1" min="11" max="11" width="8.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1196,570 +1021,479 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E2" s="1">
         <v>4.0</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="7"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1">
         <v>2.0</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="F3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="4"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1">
         <v>6.0</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1">
         <v>14.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="5"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>71</v>
+        <v>58</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O7" s="11">
-        <v>2079295.0</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1">
         <v>1.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>80</v>
+        <v>65</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>82</v>
+        <v>67</v>
+      </c>
+      <c r="M8" s="1">
+        <v>2691565.0</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2691565.0</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1">
         <v>2.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>91</v>
+        <v>74</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1">
         <v>9.0</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>98</v>
+      <c r="J10" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1">
         <v>4.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="4"/>
       <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="7"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E12" s="1">
         <v>4.0</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="F12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="4"/>
       <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="1">
         <v>1803426.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E13" s="1">
         <v>1.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="G13" s="1">
         <v>1803426.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>117</v>
+        <v>94</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>119</v>
+        <v>74</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -1767,851 +1501,718 @@
         <v>6.1300911121E10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E14" s="1">
         <v>1.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1">
         <v>6.1300911121E10</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="11">
+        <v>101</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="12">
         <v>2356161.0</v>
       </c>
-      <c r="M14" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="O14" s="5"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="7"/>
+      <c r="L14" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E15" s="1">
         <v>1.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>136</v>
+        <v>108</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>138</v>
+        <v>67</v>
+      </c>
+      <c r="M15" s="1">
+        <v>2543554.0</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O15" s="1">
-        <v>2543554.0</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1">
         <v>1.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>146</v>
+        <v>115</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O16" s="5"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="7"/>
+        <v>116</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="N16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="1">
         <v>0.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O17" s="5"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="7"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E18" s="1">
         <v>1.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>159</v>
+        <v>124</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O18" s="5"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="7"/>
+        <v>125</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18" s="5"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1">
         <v>1.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>166</v>
+        <v>129</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O19" s="5"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="7"/>
+        <v>130</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19" s="5"/>
     </row>
     <row r="20">
       <c r="A20" s="1">
         <v>50.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1">
         <v>3.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>173</v>
+        <v>134</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O20" s="5"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="7"/>
+        <v>135</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="N20" s="5"/>
     </row>
     <row r="21">
       <c r="A21" s="1">
         <v>100.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1">
         <v>1.0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>179</v>
+        <v>138</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O21" s="5"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="7"/>
+        <v>139</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M21" s="4"/>
+      <c r="N21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1">
         <v>5.0</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>186</v>
+      <c r="J22" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O22" s="5"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" s="4"/>
+      <c r="N22" s="5"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1">
         <v>2.0</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="F23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="4"/>
       <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="7"/>
     </row>
     <row r="24">
       <c r="A24" s="1">
         <v>600.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1">
         <v>1.0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>193</v>
+        <v>148</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="4"/>
+      <c r="N24" s="5"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1">
         <v>1.0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>200</v>
+        <v>153</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O25" s="5"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M25" s="4"/>
+      <c r="N25" s="5"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="E26" s="1">
         <v>2.0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>209</v>
+        <v>160</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>211</v>
+        <v>162</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="E27" s="1">
         <v>1.0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>221</v>
+        <v>169</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>223</v>
+        <v>171</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D28" s="1"/>
+        <v>174</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="E28" s="1">
         <v>1.0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L28" s="1">
+        <v>178</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="1">
         <v>3251297.0</v>
       </c>
-      <c r="M28" s="9" t="s">
-        <v>233</v>
+      <c r="L28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="E29" s="1">
         <v>1.0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>241</v>
+        <v>180</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="O29" s="5"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="N30" s="5"/>
     </row>
     <row r="34">
-      <c r="K34" s="16"/>
-      <c r="M34" s="17"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35">
-      <c r="M35" s="18"/>
-      <c r="O35" s="19"/>
+      <c r="G35" s="9"/>
+      <c r="M35" s="17"/>
     </row>
     <row r="38">
-      <c r="K38" s="20"/>
+      <c r="J38" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F3:P3"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="H11:P11"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="F3:M3"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="F12:M12"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="F23:M23"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="J2"/>
-    <hyperlink r:id="rId2" ref="M2"/>
-    <hyperlink r:id="rId3" ref="J4"/>
-    <hyperlink r:id="rId4" ref="M4"/>
-    <hyperlink r:id="rId5" ref="P4"/>
-    <hyperlink r:id="rId6" ref="J5"/>
-    <hyperlink r:id="rId7" ref="M5"/>
-    <hyperlink r:id="rId8" ref="J6"/>
-    <hyperlink r:id="rId9" ref="M6"/>
-    <hyperlink r:id="rId10" ref="J7"/>
-    <hyperlink r:id="rId11" ref="M7"/>
-    <hyperlink r:id="rId12" ref="P7"/>
-    <hyperlink r:id="rId13" ref="J8"/>
-    <hyperlink r:id="rId14" ref="M8"/>
-    <hyperlink r:id="rId15" ref="P8"/>
-    <hyperlink r:id="rId16" ref="J9"/>
-    <hyperlink r:id="rId17" ref="M9"/>
-    <hyperlink r:id="rId18" ref="P9"/>
-    <hyperlink r:id="rId19" ref="J10"/>
-    <hyperlink r:id="rId20" ref="M10"/>
-    <hyperlink r:id="rId21" ref="P10"/>
-    <hyperlink r:id="rId22" ref="J13"/>
-    <hyperlink r:id="rId23" ref="M13"/>
-    <hyperlink r:id="rId24" ref="P13"/>
-    <hyperlink r:id="rId25" ref="J14"/>
-    <hyperlink r:id="rId26" ref="M14"/>
-    <hyperlink r:id="rId27" ref="J15"/>
-    <hyperlink r:id="rId28" ref="M15"/>
-    <hyperlink r:id="rId29" ref="P15"/>
-    <hyperlink r:id="rId30" ref="J16"/>
-    <hyperlink r:id="rId31" ref="M16"/>
-    <hyperlink r:id="rId32" ref="J17"/>
-    <hyperlink r:id="rId33" ref="M17"/>
-    <hyperlink r:id="rId34" ref="J18"/>
-    <hyperlink r:id="rId35" ref="M18"/>
-    <hyperlink r:id="rId36" ref="J19"/>
-    <hyperlink r:id="rId37" ref="M19"/>
-    <hyperlink r:id="rId38" ref="J20"/>
-    <hyperlink r:id="rId39" ref="M20"/>
-    <hyperlink r:id="rId40" ref="J21"/>
-    <hyperlink r:id="rId41" ref="M21"/>
-    <hyperlink r:id="rId42" ref="J22"/>
-    <hyperlink r:id="rId43" ref="M22"/>
-    <hyperlink r:id="rId44" ref="J24"/>
-    <hyperlink r:id="rId45" ref="M24"/>
-    <hyperlink r:id="rId46" ref="J25"/>
-    <hyperlink r:id="rId47" ref="M25"/>
-    <hyperlink r:id="rId48" ref="J26"/>
-    <hyperlink r:id="rId49" ref="M26"/>
-    <hyperlink r:id="rId50" ref="P26"/>
-    <hyperlink r:id="rId51" ref="J27"/>
-    <hyperlink r:id="rId52" ref="M27"/>
-    <hyperlink r:id="rId53" ref="P27"/>
-    <hyperlink r:id="rId54" ref="J28"/>
-    <hyperlink r:id="rId55" ref="M28"/>
-    <hyperlink r:id="rId56" ref="P28"/>
-    <hyperlink r:id="rId57" ref="J29"/>
-    <hyperlink r:id="rId58" ref="M29"/>
-  </hyperlinks>
-  <drawing r:id="rId59"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>